--- a/bakup/customers/abas.xlsx
+++ b/bakup/customers/abas.xlsx
@@ -711,13 +711,13 @@
     <t>1405/05/.20</t>
   </si>
   <si>
-    <t>1405/05/23</t>
-  </si>
-  <si>
     <t>چیپس</t>
   </si>
   <si>
     <t>سیگار مغز</t>
+  </si>
+  <si>
+    <t>1405/05/26</t>
   </si>
 </sst>
 </file>
@@ -4211,10 +4211,10 @@
       </c>
       <c r="C212" s="8"/>
       <c r="D212" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4244,7 +4244,7 @@
         <v>143</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="C215" s="8"/>
       <c r="D215" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E215" s="1"/>
     </row>

--- a/bakup/customers/abas.xlsx
+++ b/bakup/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="239">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -711,13 +711,31 @@
     <t>1405/05/.20</t>
   </si>
   <si>
+    <t>1405/05/23</t>
+  </si>
+  <si>
     <t>چیپس</t>
   </si>
   <si>
     <t>سیگار مغز</t>
   </si>
   <si>
-    <t>1405/05/26</t>
+    <t>1405/05/24</t>
+  </si>
+  <si>
+    <t>1405/05/31</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
+  </si>
+  <si>
+    <t>اوسکار</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1292,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4211,10 +4229,10 @@
       </c>
       <c r="C212" s="8"/>
       <c r="D212" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4244,7 +4262,7 @@
         <v>143</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4257,54 +4275,78 @@
       </c>
       <c r="C215" s="8"/>
       <c r="D215" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E215" s="1"/>
     </row>
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B216" s="8"/>
+        <v>3317000</v>
+      </c>
+      <c r="B216" s="8">
+        <v>25000</v>
+      </c>
       <c r="C216" s="8"/>
-      <c r="D216" s="1"/>
-      <c r="E216" s="1"/>
+      <c r="D216" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B217" s="8"/>
+        <v>3388000</v>
+      </c>
+      <c r="B217" s="8">
+        <v>71000</v>
+      </c>
       <c r="C217" s="8"/>
-      <c r="D217" s="1"/>
-      <c r="E217" s="1"/>
+      <c r="D217" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B218" s="8"/>
+        <v>3577000</v>
+      </c>
+      <c r="B218" s="8">
+        <v>189000</v>
+      </c>
       <c r="C218" s="8"/>
-      <c r="D218" s="1"/>
-      <c r="E218" s="1"/>
+      <c r="D218" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B219" s="8"/>
+        <v>3677000</v>
+      </c>
+      <c r="B219" s="8">
+        <v>100000</v>
+      </c>
       <c r="C219" s="8"/>
-      <c r="D219" s="1"/>
-      <c r="E219" s="1"/>
+      <c r="D219" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4314,7 +4356,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4324,7 +4366,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4334,7 +4376,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4344,7 +4386,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4354,7 +4396,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4364,7 +4406,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4374,7 +4416,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4384,7 +4426,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4394,7 +4436,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4404,7 +4446,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12490500</v>
+        <v>12875500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4415,7 +4457,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>
